--- a/dataset/construct/dataset_splits/data_size/10_percent/merged/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/merged/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,85 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.2467825500038</v>
+        <v>84.97033370725281</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>30.1109905115367</v>
       </c>
       <c r="E2" t="n">
-        <v>30.3460743801652</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I2" t="n">
-        <v>3370</v>
+        <v>152</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="K2" t="n">
-        <v>242.8</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>371.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>285.3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>899.4</v>
+        <v>98</v>
       </c>
       <c r="O2" t="n">
-        <v>72.3</v>
+        <v>98</v>
       </c>
       <c r="P2" t="n">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>264.3</v>
+        <v>96</v>
       </c>
       <c r="S2" t="n">
-        <v>22.6</v>
+        <v>96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>53.2</v>
+        <v>24.3</v>
       </c>
       <c r="V2" t="n">
-        <v>75.8</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X2" t="n">
-        <v>26.9</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.16382252559727</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>26.8217134966894</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -730,31 +715,24 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>566</v>
+        <v>612</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,40 +740,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>84.7733230663929</v>
+        <v>82.2897330595483</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="E3" t="n">
-        <v>20.829995193078</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="I3" t="n">
-        <v>1480</v>
+        <v>39.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>32.1</v>
       </c>
       <c r="K3" t="n">
-        <v>193</v>
+        <v>263.9</v>
       </c>
       <c r="L3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>283.8</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -813,34 +791,34 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X3" t="n">
-        <v>22.7</v>
+        <v>22.0244421422418</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.198412698412698</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7909345556404</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.4508627838174</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -849,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -861,22 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1094</v>
+        <v>1306</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,79 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.44095254391971</v>
+        <v>86.2350005070094</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>21.6855368882395</v>
       </c>
       <c r="E4" t="n">
-        <v>25.3443526170798</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>10.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1550</v>
+        <v>136.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>420.7</v>
+        <v>220.2</v>
       </c>
       <c r="L4" t="n">
-        <v>199.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>296.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>916.7</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>35.2</v>
+        <v>20.85</v>
       </c>
       <c r="V4" t="n">
-        <v>35.2</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>20.912910618793</v>
       </c>
       <c r="X4" t="n">
-        <v>23.25</v>
+        <v>20.4698827870943</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.204633204633205</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.3002291825821</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.8943655965997</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
@@ -971,36 +942,27 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2031</v>
+        <v>624</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,79 +970,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>85.6764691865034</v>
+        <v>90.1065803483155</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>20.0288415318058</v>
       </c>
       <c r="E5" t="n">
-        <v>27.7777777777777</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
-        <v>882</v>
+        <v>45</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
-        <v>423.4</v>
+        <v>156</v>
       </c>
       <c r="L5" t="n">
-        <v>142.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>389.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>955.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>55.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>198.5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>65.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>27.2</v>
+        <v>22.15</v>
       </c>
       <c r="V5" t="n">
-        <v>92.59999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X5" t="n">
-        <v>28.85</v>
+        <v>21.9926337013585</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.235474006116208</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.4435956200662</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>28.5191036537487</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,22 +1069,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>208</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>551</v>
+        <v>2012</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,88 +1085,88 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.878606738155</v>
+        <v>84.8005503270211</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>25.5102040816326</v>
       </c>
       <c r="E6" t="n">
-        <v>23.1481481481481</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>564.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1010</v>
+        <v>316.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>120.3</v>
       </c>
       <c r="K6" t="n">
-        <v>852</v>
+        <v>1001.9</v>
       </c>
       <c r="L6" t="n">
-        <v>377</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>892</v>
+        <v>6.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2121</v>
+        <v>15.3</v>
       </c>
       <c r="O6" t="n">
-        <v>300</v>
+        <v>116.3</v>
       </c>
       <c r="P6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>204</v>
+        <v>24.85</v>
       </c>
       <c r="V6" t="n">
-        <v>474</v>
+        <v>0.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>25.9103641456583</v>
       </c>
       <c r="X6" t="n">
-        <v>23.7</v>
+        <v>24.8126692377086</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.197718631178707</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.5033791921504</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1220,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1229,24 +1184,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>234</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>914</v>
+        <v>1427</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,79 +1200,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.0671732958146</v>
+        <v>86.99098473901689</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.2080856123662</v>
       </c>
       <c r="E7" t="n">
-        <v>25.7629805786761</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>319.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>264.3</v>
       </c>
       <c r="K7" t="n">
-        <v>855</v>
+        <v>786.8</v>
       </c>
       <c r="L7" t="n">
-        <v>534</v>
+        <v>36.6</v>
       </c>
       <c r="M7" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>36.6</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>93</v>
+        <v>22.35</v>
       </c>
       <c r="V7" t="n">
-        <v>93</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.0137509549274</v>
       </c>
       <c r="X7" t="n">
-        <v>29</v>
+        <v>22.1512191514658</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.220858895705522</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>29.921059332824</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>29.2679951700071</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,28 +1293,21 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
         <v>154</v>
       </c>
-      <c r="AN7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54822613</v>
+        <v>54380016</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,74 +1315,80 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64.34496919917861</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>82.3299110198494</v>
+      </c>
+      <c r="D8" t="n">
+        <v>33.2179930795848</v>
+      </c>
       <c r="E8" t="n">
-        <v>34.6666666666667</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45</v>
+      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
-        <v>50</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>419</v>
+      </c>
+      <c r="M8" t="n">
+        <v>133</v>
+      </c>
+      <c r="N8" t="n">
+        <v>100</v>
+      </c>
       <c r="O8" t="n">
-        <v>251</v>
+        <v>652</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>41</v>
+        <v>25.1</v>
       </c>
       <c r="V8" t="n">
-        <v>41</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>25.14648100851947</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>24.59245379682967</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>63.9</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>314.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1452,33 +1397,24 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>174</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53731161</v>
+        <v>51310921</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1486,74 +1422,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>87.4661190965092</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>82.76796714579049</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23.8086901719128</v>
+      </c>
       <c r="E9" t="n">
-        <v>24.3374797187669</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>414</v>
+      </c>
+      <c r="I9" t="n">
+        <v>322</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="K9" t="n">
+        <v>986</v>
+      </c>
+      <c r="L9" t="n">
+        <v>414</v>
+      </c>
+      <c r="M9" t="n">
+        <v>322</v>
+      </c>
+      <c r="N9" t="n">
+        <v>221</v>
+      </c>
       <c r="O9" t="n">
-        <v>489.90607</v>
+        <v>957</v>
       </c>
       <c r="P9" t="n">
-        <v>244.57335</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>201.23125</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>935.71075</v>
+        <v>225</v>
       </c>
       <c r="S9" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>35</v>
+        <v>27.6</v>
       </c>
       <c r="V9" t="n">
-        <v>263</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>28.52056580206764</v>
       </c>
       <c r="X9" t="n">
-        <v>24.043266</v>
+        <v>27.79113361913022</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>78.1448</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>470.0287</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1571,20 +1521,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+        <v>182</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53291409</v>
+        <v>53146249</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1592,84 +1537,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>81.79329226557149</v>
+        <v>74.03969883641339</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>29.0687961508904</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45</v>
+      </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>1326</v>
+      </c>
+      <c r="I10" t="n">
+        <v>773</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>426</v>
       </c>
       <c r="K10" t="n">
-        <v>310</v>
+        <v>2525</v>
       </c>
       <c r="L10" t="n">
-        <v>66</v>
+        <v>1320</v>
       </c>
       <c r="M10" t="n">
-        <v>63</v>
+        <v>718</v>
       </c>
       <c r="N10" t="n">
-        <v>439</v>
+        <v>384</v>
       </c>
       <c r="O10" t="n">
-        <v>310</v>
+        <v>2422</v>
       </c>
       <c r="P10" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="Q10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>425</v>
+        <v>61</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>26.03774868983408</v>
       </c>
       <c r="X10" t="n">
-        <v>23.1</v>
+        <v>24.58986498122201</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>74.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1681,26 +1630,21 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+        <v>109</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54786923</v>
+        <v>54397745</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1708,74 +1652,80 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74.4284736481862</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>91.668720054757</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25.2173585757838</v>
+      </c>
       <c r="E11" t="n">
-        <v>25.013520822066</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>252</v>
+      </c>
+      <c r="M11" t="n">
+        <v>110</v>
+      </c>
+      <c r="N11" t="n">
+        <v>324</v>
+      </c>
       <c r="O11" t="n">
-        <v>115</v>
+        <v>686</v>
       </c>
       <c r="P11" t="n">
-        <v>188</v>
+        <v>420</v>
       </c>
       <c r="Q11" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>474</v>
+        <v>202</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>22.72732587352266</v>
       </c>
       <c r="X11" t="n">
-        <v>25.6</v>
+        <v>21.03753944143522</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>86.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1787,30 +1737,21 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53683397</v>
+        <v>53324217</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1818,84 +1759,88 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82.2149212867899</v>
+        <v>78.8227241615332</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>25.3515413737155</v>
       </c>
       <c r="E12" t="n">
-        <v>27.0538027739674</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>284</v>
+      </c>
+      <c r="I12" t="n">
+        <v>215</v>
+      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="K12" t="n">
-        <v>457</v>
+        <v>666</v>
       </c>
       <c r="L12" t="n">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="M12" t="n">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>781</v>
+        <v>93</v>
       </c>
       <c r="O12" t="n">
-        <v>457</v>
+        <v>419</v>
       </c>
       <c r="P12" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>27.02450933700383</v>
       </c>
       <c r="X12" t="n">
-        <v>24.1</v>
+        <v>25.9134431500973</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>79.8</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>463.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1904,33 +1849,24 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>159</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>53940332</v>
+        <v>53688310</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1938,71 +1874,85 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>89.42915811088299</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>92.7775496235455</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30.4498269896194</v>
+      </c>
       <c r="E13" t="n">
-        <v>24.2214532871972</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>683</v>
+      </c>
+      <c r="I13" t="n">
+        <v>643</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>414</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1740</v>
+      </c>
+      <c r="L13" t="n">
+        <v>683</v>
+      </c>
+      <c r="M13" t="n">
+        <v>574</v>
+      </c>
+      <c r="N13" t="n">
+        <v>408</v>
+      </c>
       <c r="O13" t="n">
-        <v>116</v>
+        <v>1665</v>
       </c>
       <c r="P13" t="n">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="Q13" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>428</v>
+        <v>11</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>0.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>26.57887549634652</v>
       </c>
       <c r="X13" t="n">
-        <v>21.4</v>
+        <v>26.20416162512499</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>380.1</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2011,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2020,27 +1970,14 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>128</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53592996</v>
+        <v>53959319</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2048,84 +1985,80 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>81.8617385352498</v>
+        <v>82.8637919233402</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>24.7251829329413</v>
       </c>
       <c r="E14" t="n">
-        <v>27.4692816635161</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>55</v>
+      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
-        <v>37</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1122</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>512</v>
+        <v>331</v>
       </c>
       <c r="M14" t="n">
-        <v>1058</v>
+        <v>197</v>
       </c>
       <c r="N14" t="n">
-        <v>2692</v>
+        <v>113</v>
       </c>
       <c r="O14" t="n">
-        <v>1043</v>
+        <v>641</v>
       </c>
       <c r="P14" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1058</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2608</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>307</v>
+        <v>24.1</v>
       </c>
       <c r="V14" t="n">
-        <v>352</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>25.4011289174665</v>
       </c>
       <c r="X14" t="n">
-        <v>31.5</v>
+        <v>24.50428063210799</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>105.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2143,24 +2076,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>186</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>109</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54742613</v>
+        <v>54859265</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2168,109 +2092,106 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72.1587953456537</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>70.1054072553046</v>
+      </c>
+      <c r="D15" t="n">
+        <v>29.9616116850286</v>
+      </c>
       <c r="E15" t="n">
-        <v>30.8979120501857</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>55</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>47</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>626</v>
+      </c>
+      <c r="M15" t="n">
+        <v>315</v>
+      </c>
+      <c r="N15" t="n">
+        <v>291</v>
+      </c>
       <c r="O15" t="n">
-        <v>203</v>
+        <v>1232</v>
       </c>
       <c r="P15" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>27.47014317766114</v>
       </c>
       <c r="X15" t="n">
-        <v>25.5</v>
+        <v>26.53730943771464</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>80.5</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>498.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>177</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>52530187</v>
+        <v>52386464</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2278,121 +2199,114 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>78.5516769336071</v>
+        <v>82.11909650924029</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>24.3827160493827</v>
       </c>
       <c r="E16" t="n">
-        <v>27.9296875</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="I16" t="n">
+        <v>546</v>
+      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="K16" t="n">
-        <v>96</v>
+        <v>1171</v>
       </c>
       <c r="L16" t="n">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="M16" t="n">
-        <v>258</v>
+        <v>540</v>
       </c>
       <c r="N16" t="n">
-        <v>433</v>
+        <v>368</v>
       </c>
       <c r="O16" t="n">
-        <v>72</v>
+        <v>1151</v>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="S16" t="n">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>19</v>
+        <v>30.6</v>
       </c>
       <c r="V16" t="n">
-        <v>155</v>
+        <v>0.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>31.73549565252393</v>
       </c>
       <c r="X16" t="n">
-        <v>24.5</v>
+        <v>31.00887782851864</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>442.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>126</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>51748563</v>
+        <v>54879462</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2400,121 +2314,106 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80.46269678302529</v>
+        <v>81.138945927447</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>32.4499729583559</v>
       </c>
       <c r="E17" t="n">
-        <v>25.390625</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>47</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="M17" t="n">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="N17" t="n">
-        <v>744</v>
+        <v>534</v>
       </c>
       <c r="O17" t="n">
-        <v>47</v>
+        <v>1135</v>
       </c>
       <c r="P17" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>25.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>27.18366428009573</v>
       </c>
       <c r="X17" t="n">
-        <v>24.8</v>
+        <v>26.14091933462482</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>461.6</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>51721443</v>
+        <v>52588750</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2522,119 +2421,114 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>83.8685831622177</v>
+        <v>75.9260780287474</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>24.6913580246914</v>
       </c>
       <c r="E18" t="n">
-        <v>26.4721074380165</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>552</v>
+      </c>
+      <c r="I18" t="n">
+        <v>563</v>
+      </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="K18" t="n">
-        <v>910</v>
+        <v>1540</v>
       </c>
       <c r="L18" t="n">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="M18" t="n">
-        <v>808</v>
+        <v>496</v>
       </c>
       <c r="N18" t="n">
-        <v>2298</v>
+        <v>425</v>
       </c>
       <c r="O18" t="n">
-        <v>910</v>
+        <v>1452</v>
       </c>
       <c r="P18" t="n">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2018</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>31.86281960699744</v>
       </c>
       <c r="X18" t="n">
-        <v>29.5</v>
+        <v>30.32801093241496</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>93.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>647.7</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>124</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54153818</v>
+        <v>51437724</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2642,65 +2536,69 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>79.7891854893908</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>89.8179329226557</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.8359096313912</v>
+      </c>
       <c r="E19" t="n">
-        <v>32.6293520742945</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>245.42831</v>
+      </c>
+      <c r="M19" t="n">
+        <v>174.54457</v>
+      </c>
+      <c r="N19" t="n">
+        <v>138.30325</v>
+      </c>
       <c r="O19" t="n">
-        <v>175</v>
+        <v>558.27613</v>
       </c>
       <c r="P19" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>24.227337</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>24.40130674242708</v>
       </c>
       <c r="X19" t="n">
-        <v>23.6</v>
+        <v>23.98987581932773</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>76.3</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>445.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2709,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2718,33 +2616,20 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>144</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>110</v>
-      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>53955359</v>
+        <v>52800188</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2752,74 +2637,88 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>83.6714579055441</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>93.68104038329911</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23.4256055363322</v>
+      </c>
       <c r="E20" t="n">
-        <v>19.8791026005112</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>55</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="I20" t="n">
+        <v>130</v>
+      </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>112</v>
+      </c>
+      <c r="K20" t="n">
+        <v>525</v>
+      </c>
+      <c r="L20" t="n">
+        <v>247</v>
+      </c>
+      <c r="M20" t="n">
+        <v>130</v>
+      </c>
+      <c r="N20" t="n">
+        <v>102</v>
+      </c>
       <c r="O20" t="n">
-        <v>126</v>
+        <v>479</v>
       </c>
       <c r="P20" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="Q20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>26.8</v>
       </c>
       <c r="V20" t="n">
-        <v>135</v>
+        <v>0.17</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>27.02450933700383</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>26.76424046872996</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>70.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>377.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2831,30 +2730,17 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>150</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>55642168</v>
+        <v>55333786</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2862,65 +2748,71 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82.4695414099932</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>86.7433264887064</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19.0311418685121</v>
+      </c>
       <c r="E21" t="n">
-        <v>24.5778671518401</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>52</v>
+      </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>341</v>
+      </c>
+      <c r="M21" t="n">
+        <v>320</v>
+      </c>
+      <c r="N21" t="n">
+        <v>374</v>
+      </c>
       <c r="O21" t="n">
-        <v>435.7692</v>
+        <v>1035</v>
       </c>
       <c r="P21" t="n">
-        <v>471.15186</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>348.57095</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1255.492</v>
+        <v>161</v>
       </c>
       <c r="S21" t="n">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>175</v>
+        <v>22.8</v>
       </c>
       <c r="V21" t="n">
-        <v>226</v>
+        <v>0.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>27.34281922318762</v>
       </c>
       <c r="X21" t="n">
-        <v>27.29889</v>
+        <v>23.64216910815792</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>86.90398999999999</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>573.0519</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2941,25 +2833,16 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
